--- a/EPTS Test Cases/API Test Cases/Login.xlsx
+++ b/EPTS Test Cases/API Test Cases/Login.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srinivas\Desktop\MogoMantra Project\EPTS\EPTS Test Cases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srinivas\Desktop\MogoMantra Project\EPTS Testing\EPTS Test Cases\API Test Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB6B1406-5995-40FA-94F6-B59E5F3FEAE5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCF1BCB3-A9E9-4BA9-BC6C-3A1301B18B00}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="89">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -284,6 +284,15 @@
   </si>
   <si>
     <t xml:space="preserve">405 Method Not Allowed </t>
+  </si>
+  <si>
+    <t>Initial Test Result</t>
+  </si>
+  <si>
+    <t>1st Retest Result</t>
+  </si>
+  <si>
+    <t>Account has been locked, try again after 1 Hr</t>
   </si>
 </sst>
 </file>
@@ -361,7 +370,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -384,11 +393,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -421,6 +439,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -702,7 +726,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A5:K18"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.5703125" customWidth="1"/>
@@ -710,17 +734,69 @@
     <col min="4" max="8" width="16.5703125" customWidth="1"/>
     <col min="9" max="9" width="15.42578125" customWidth="1"/>
     <col min="10" max="10" width="12.5703125" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" customWidth="1"/>
+    <col min="13" max="13" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I1" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>75</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+    </row>
+    <row r="7" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
@@ -754,8 +830,17 @@
       <c r="K7" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>6</v>
       </c>
@@ -789,8 +874,17 @@
       <c r="K8" s="2" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
@@ -824,8 +918,17 @@
       <c r="K9" s="6" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L9" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
         <v>17</v>
       </c>
@@ -859,8 +962,17 @@
       <c r="K10" s="6" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L10" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>21</v>
       </c>
@@ -894,8 +1006,17 @@
       <c r="K11" s="6" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L11" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>27</v>
       </c>
@@ -929,8 +1050,17 @@
       <c r="K12" s="6" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L12" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>32</v>
       </c>
@@ -964,8 +1094,17 @@
       <c r="K13" s="6" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L13" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>37</v>
       </c>
@@ -999,8 +1138,17 @@
       <c r="K14" s="6" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>42</v>
       </c>
@@ -1034,8 +1182,17 @@
       <c r="K15" s="6" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>47</v>
       </c>
@@ -1069,8 +1226,17 @@
       <c r="K16" s="6" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L16" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>50</v>
       </c>
@@ -1104,8 +1270,17 @@
       <c r="K17" s="6" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L17" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N17" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>55</v>
       </c>
@@ -1139,8 +1314,21 @@
       <c r="K18" s="6" t="s">
         <v>71</v>
       </c>
+      <c r="L18" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>67</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="I1:K6"/>
+    <mergeCell ref="L1:N6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
@@ -1150,7 +1338,7 @@
           <x14:formula1>
             <xm:f>Sheet2!$C$3:$C$5</xm:f>
           </x14:formula1>
-          <xm:sqref>K8:K18</xm:sqref>
+          <xm:sqref>K8:K18 N8:N18</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
